--- a/stacked_model/results/validation/deployed_stack_config/deployed_stack_fold_results.xlsx
+++ b/stacked_model/results/validation/deployed_stack_config/deployed_stack_fold_results.xlsx
@@ -560,7 +560,7 @@
         <v>0</v>
       </c>
       <c r="D2" t="n">
-        <v>1e-06</v>
+        <v>0.01</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
@@ -592,7 +592,7 @@
         <v>0</v>
       </c>
       <c r="L2" t="n">
-        <v>1e-06</v>
+        <v>0.01</v>
       </c>
       <c r="M2" t="n">
         <v>1</v>
@@ -604,28 +604,28 @@
         <v>38</v>
       </c>
       <c r="P2" t="n">
-        <v>2.028276421337497</v>
+        <v>2.467534444847869</v>
       </c>
       <c r="Q2" t="n">
-        <v>2.795382267260514</v>
+        <v>3.247811934055953</v>
       </c>
       <c r="R2" t="n">
-        <v>0.9644751452920067</v>
+        <v>0.9390009479600042</v>
       </c>
       <c r="S2" t="n">
-        <v>0.8947368421052632</v>
+        <v>0.868421052631579</v>
       </c>
       <c r="T2" t="n">
-        <v>2.569783335524105</v>
+        <v>2.652961293267559</v>
       </c>
       <c r="U2" t="n">
-        <v>-186.9210674686247</v>
+        <v>-178.0322606814804</v>
       </c>
       <c r="V2" t="n">
-        <v>-122.4417898552794</v>
+        <v>-119.1535784943637</v>
       </c>
       <c r="W2" t="n">
-        <v>-64.47927761334529</v>
+        <v>-58.87868218711674</v>
       </c>
     </row>
     <row r="3">
@@ -643,7 +643,7 @@
         <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>1e-06</v>
+        <v>0.01</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
@@ -675,7 +675,7 @@
         <v>0</v>
       </c>
       <c r="L3" t="n">
-        <v>1e-06</v>
+        <v>0.01</v>
       </c>
       <c r="M3" t="n">
         <v>2</v>
@@ -687,28 +687,28 @@
         <v>38</v>
       </c>
       <c r="P3" t="n">
-        <v>3.089717911460483</v>
+        <v>3.187896029899177</v>
       </c>
       <c r="Q3" t="n">
-        <v>4.10302822191091</v>
+        <v>4.209590760365135</v>
       </c>
       <c r="R3" t="n">
-        <v>0.9116292014757369</v>
+        <v>0.9098871864111856</v>
       </c>
       <c r="S3" t="n">
-        <v>0.868421052631579</v>
+        <v>0.7894736842105263</v>
       </c>
       <c r="T3" t="n">
-        <v>2.99203941215106</v>
+        <v>3.258027001628874</v>
       </c>
       <c r="U3" t="n">
-        <v>-181.5408716432798</v>
+        <v>-181.4331300144417</v>
       </c>
       <c r="V3" t="n">
-        <v>-123.6577566871383</v>
+        <v>-123.4108984323706</v>
       </c>
       <c r="W3" t="n">
-        <v>-57.8831149561415</v>
+        <v>-58.02223158207109</v>
       </c>
     </row>
     <row r="4">
@@ -726,7 +726,7 @@
         <v>0</v>
       </c>
       <c r="D4" t="n">
-        <v>1e-06</v>
+        <v>0.01</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
@@ -758,7 +758,7 @@
         <v>0</v>
       </c>
       <c r="L4" t="n">
-        <v>1e-06</v>
+        <v>0.01</v>
       </c>
       <c r="M4" t="n">
         <v>3</v>
@@ -770,28 +770,28 @@
         <v>38</v>
       </c>
       <c r="P4" t="n">
-        <v>4.009029055229816</v>
+        <v>3.235095665006958</v>
       </c>
       <c r="Q4" t="n">
-        <v>6.027192948259752</v>
+        <v>4.371970914872202</v>
       </c>
       <c r="R4" t="n">
-        <v>0.8343185476173161</v>
+        <v>0.9164481116233449</v>
       </c>
       <c r="S4" t="n">
-        <v>0.868421052631579</v>
+        <v>0.9210526315789473</v>
       </c>
       <c r="T4" t="n">
-        <v>2.858911165334865</v>
+        <v>2.738208893190154</v>
       </c>
       <c r="U4" t="n">
-        <v>-168.9692137919621</v>
+        <v>-166.0743607835526</v>
       </c>
       <c r="V4" t="n">
-        <v>-112.7848250419511</v>
+        <v>-111.2423279364433</v>
       </c>
       <c r="W4" t="n">
-        <v>-56.18438875001105</v>
+        <v>-54.8320328471093</v>
       </c>
     </row>
     <row r="5">
@@ -809,7 +809,7 @@
         <v>0</v>
       </c>
       <c r="D5" t="n">
-        <v>1e-06</v>
+        <v>0.01</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
@@ -841,7 +841,7 @@
         <v>0</v>
       </c>
       <c r="L5" t="n">
-        <v>1e-06</v>
+        <v>0.01</v>
       </c>
       <c r="M5" t="n">
         <v>4</v>
@@ -853,28 +853,28 @@
         <v>38</v>
       </c>
       <c r="P5" t="n">
-        <v>4.284158811659039</v>
+        <v>4.200817963430168</v>
       </c>
       <c r="Q5" t="n">
-        <v>8.732932212263655</v>
+        <v>8.819747079938423</v>
       </c>
       <c r="R5" t="n">
-        <v>0.5475872515059084</v>
+        <v>0.5373078556130113</v>
       </c>
       <c r="S5" t="n">
         <v>0.868421052631579</v>
       </c>
       <c r="T5" t="n">
-        <v>3.64778039243231</v>
+        <v>3.772374609194014</v>
       </c>
       <c r="U5" t="n">
-        <v>-152.91161548311</v>
+        <v>-154.2709117516987</v>
       </c>
       <c r="V5" t="n">
-        <v>-115.1351798226488</v>
+        <v>-116.9166626714119</v>
       </c>
       <c r="W5" t="n">
-        <v>-37.7764356604613</v>
+        <v>-37.35424908028689</v>
       </c>
     </row>
     <row r="6">
@@ -892,7 +892,7 @@
         <v>0</v>
       </c>
       <c r="D6" t="n">
-        <v>1e-06</v>
+        <v>0.01</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
@@ -924,7 +924,7 @@
         <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>1e-06</v>
+        <v>0.01</v>
       </c>
       <c r="M6" t="n">
         <v>5</v>
@@ -936,28 +936,28 @@
         <v>38</v>
       </c>
       <c r="P6" t="n">
-        <v>3.156982989524257</v>
+        <v>4.333580888408722</v>
       </c>
       <c r="Q6" t="n">
-        <v>4.511176073747119</v>
+        <v>6.864462313772571</v>
       </c>
       <c r="R6" t="n">
-        <v>0.8841531789080129</v>
+        <v>0.747413430704899</v>
       </c>
       <c r="S6" t="n">
-        <v>0.8421052631578947</v>
+        <v>0.6578947368421053</v>
       </c>
       <c r="T6" t="n">
-        <v>2.912893437997214</v>
+        <v>3.55217636749733</v>
       </c>
       <c r="U6" t="n">
-        <v>-171.9601067576271</v>
+        <v>-172.6900396437304</v>
       </c>
       <c r="V6" t="n">
-        <v>-111.2847329197141</v>
+        <v>-115.3002501370646</v>
       </c>
       <c r="W6" t="n">
-        <v>-60.67537383791306</v>
+        <v>-57.38978950666578</v>
       </c>
     </row>
     <row r="7">
@@ -975,7 +975,7 @@
         <v>0</v>
       </c>
       <c r="D7" t="n">
-        <v>1e-06</v>
+        <v>0.01</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
@@ -1007,7 +1007,7 @@
         <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>1e-06</v>
+        <v>0.01</v>
       </c>
       <c r="M7" t="n">
         <v>6</v>
@@ -1019,28 +1019,28 @@
         <v>38</v>
       </c>
       <c r="P7" t="n">
-        <v>3.976357260008071</v>
+        <v>3.727122849744092</v>
       </c>
       <c r="Q7" t="n">
-        <v>5.873572707282979</v>
+        <v>5.555102796303983</v>
       </c>
       <c r="R7" t="n">
-        <v>0.7966052022688948</v>
+        <v>0.8255371751108981</v>
       </c>
       <c r="S7" t="n">
-        <v>0.7631578947368421</v>
+        <v>0.7368421052631579</v>
       </c>
       <c r="T7" t="n">
-        <v>3.411724208809004</v>
+        <v>3.367655903118274</v>
       </c>
       <c r="U7" t="n">
-        <v>-166.8945741735404</v>
+        <v>-166.6107833257836</v>
       </c>
       <c r="V7" t="n">
-        <v>-121.9228617576505</v>
+        <v>-119.1003934268013</v>
       </c>
       <c r="W7" t="n">
-        <v>-44.97171241588988</v>
+        <v>-47.51038989898224</v>
       </c>
     </row>
     <row r="8">
@@ -1058,7 +1058,7 @@
         <v>0</v>
       </c>
       <c r="D8" t="n">
-        <v>1e-06</v>
+        <v>0.01</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
@@ -1090,7 +1090,7 @@
         <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>1e-06</v>
+        <v>0.01</v>
       </c>
       <c r="M8" t="n">
         <v>7</v>
@@ -1102,28 +1102,28 @@
         <v>38</v>
       </c>
       <c r="P8" t="n">
-        <v>4.567633501467689</v>
+        <v>2.458650158565442</v>
       </c>
       <c r="Q8" t="n">
-        <v>6.469605257333066</v>
+        <v>3.202070770378133</v>
       </c>
       <c r="R8" t="n">
-        <v>0.7926836675691558</v>
+        <v>0.9415504372602672</v>
       </c>
       <c r="S8" t="n">
-        <v>0.8157894736842105</v>
+        <v>0.9210526315789473</v>
       </c>
       <c r="T8" t="n">
-        <v>3.394142803553662</v>
+        <v>2.713182588515705</v>
       </c>
       <c r="U8" t="n">
-        <v>-170.738862579812</v>
+        <v>-174.3757947568558</v>
       </c>
       <c r="V8" t="n">
-        <v>-116.0070343690476</v>
+        <v>-114.1021395629864</v>
       </c>
       <c r="W8" t="n">
-        <v>-54.73182821076439</v>
+        <v>-60.27365519386937</v>
       </c>
     </row>
     <row r="9">
@@ -1141,7 +1141,7 @@
         <v>0</v>
       </c>
       <c r="D9" t="n">
-        <v>1e-06</v>
+        <v>0.01</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
@@ -1173,7 +1173,7 @@
         <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>1e-06</v>
+        <v>0.01</v>
       </c>
       <c r="M9" t="n">
         <v>8</v>
@@ -1185,28 +1185,28 @@
         <v>38</v>
       </c>
       <c r="P9" t="n">
-        <v>3.764193719686416</v>
+        <v>4.465730512240301</v>
       </c>
       <c r="Q9" t="n">
-        <v>6.1112923439156</v>
+        <v>6.646990718984054</v>
       </c>
       <c r="R9" t="n">
-        <v>0.8397103817003244</v>
+        <v>0.8045818278365214</v>
       </c>
       <c r="S9" t="n">
-        <v>0.8157894736842105</v>
+        <v>0.7894736842105263</v>
       </c>
       <c r="T9" t="n">
-        <v>3.113520621482067</v>
+        <v>3.283955372875474</v>
       </c>
       <c r="U9" t="n">
-        <v>-179.2824790165988</v>
+        <v>-182.1982475549533</v>
       </c>
       <c r="V9" t="n">
-        <v>-114.4885784402329</v>
+        <v>-119.6787802513089</v>
       </c>
       <c r="W9" t="n">
-        <v>-64.79390057636583</v>
+        <v>-62.5194673036444</v>
       </c>
     </row>
     <row r="10">
@@ -1224,7 +1224,7 @@
         <v>0</v>
       </c>
       <c r="D10" t="n">
-        <v>1e-06</v>
+        <v>0.01</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
@@ -1256,7 +1256,7 @@
         <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>1e-06</v>
+        <v>0.01</v>
       </c>
       <c r="M10" t="n">
         <v>9</v>
@@ -1268,28 +1268,28 @@
         <v>38</v>
       </c>
       <c r="P10" t="n">
-        <v>4.114904239625824</v>
+        <v>3.241683366424146</v>
       </c>
       <c r="Q10" t="n">
-        <v>6.261354471033019</v>
+        <v>4.869662803380247</v>
       </c>
       <c r="R10" t="n">
-        <v>0.80310156955409</v>
+        <v>0.8887484442000932</v>
       </c>
       <c r="S10" t="n">
-        <v>0.9210526315789473</v>
+        <v>0.8947368421052632</v>
       </c>
       <c r="T10" t="n">
-        <v>2.903177498008637</v>
+        <v>2.878198536447836</v>
       </c>
       <c r="U10" t="n">
-        <v>-183.3578302275511</v>
+        <v>-186.0637182745993</v>
       </c>
       <c r="V10" t="n">
-        <v>-124.7294241588194</v>
+        <v>-123.6716555652983</v>
       </c>
       <c r="W10" t="n">
-        <v>-58.62840606873171</v>
+        <v>-62.39206270930103</v>
       </c>
     </row>
     <row r="11">
@@ -1307,7 +1307,7 @@
         <v>0</v>
       </c>
       <c r="D11" t="n">
-        <v>1e-06</v>
+        <v>0.01</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
@@ -1339,7 +1339,7 @@
         <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>1e-06</v>
+        <v>0.01</v>
       </c>
       <c r="M11" t="n">
         <v>10</v>
@@ -1351,28 +1351,28 @@
         <v>38</v>
       </c>
       <c r="P11" t="n">
-        <v>2.554919966634869</v>
+        <v>3.615410215749524</v>
       </c>
       <c r="Q11" t="n">
-        <v>3.435699945788328</v>
+        <v>6.122392489030665</v>
       </c>
       <c r="R11" t="n">
-        <v>0.9359163088703291</v>
+        <v>0.7973900547035655</v>
       </c>
       <c r="S11" t="n">
-        <v>0.868421052631579</v>
+        <v>0.7631578947368421</v>
       </c>
       <c r="T11" t="n">
-        <v>2.656411192467226</v>
+        <v>3.047571849275269</v>
       </c>
       <c r="U11" t="n">
-        <v>-167.0442535411858</v>
+        <v>-162.6915613625443</v>
       </c>
       <c r="V11" t="n">
-        <v>-112.8604065077421</v>
+        <v>-112.3845673577484</v>
       </c>
       <c r="W11" t="n">
-        <v>-54.1838470334437</v>
+        <v>-50.30699400479591</v>
       </c>
     </row>
     <row r="12">
@@ -1390,7 +1390,7 @@
         <v>0</v>
       </c>
       <c r="D12" t="n">
-        <v>1e-06</v>
+        <v>0.01</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
@@ -1422,7 +1422,7 @@
         <v>0</v>
       </c>
       <c r="L12" t="n">
-        <v>1e-06</v>
+        <v>0.01</v>
       </c>
       <c r="M12" t="n">
         <v>11</v>
@@ -1434,28 +1434,28 @@
         <v>38</v>
       </c>
       <c r="P12" t="n">
-        <v>2.895310681256621</v>
+        <v>3.107208429140492</v>
       </c>
       <c r="Q12" t="n">
-        <v>4.445493447341658</v>
+        <v>4.50142908688374</v>
       </c>
       <c r="R12" t="n">
-        <v>0.9025974580198853</v>
+        <v>0.9064406825641377</v>
       </c>
       <c r="S12" t="n">
-        <v>0.8947368421052632</v>
+        <v>0.8421052631578947</v>
       </c>
       <c r="T12" t="n">
-        <v>2.734550542593082</v>
+        <v>2.921086174988108</v>
       </c>
       <c r="U12" t="n">
-        <v>-170.6531470858885</v>
+        <v>-181.1706150293361</v>
       </c>
       <c r="V12" t="n">
-        <v>-115.3426898188819</v>
+        <v>-119.2026009954407</v>
       </c>
       <c r="W12" t="n">
-        <v>-55.31045726700657</v>
+        <v>-61.96801403389536</v>
       </c>
     </row>
     <row r="13">
@@ -1473,7 +1473,7 @@
         <v>0</v>
       </c>
       <c r="D13" t="n">
-        <v>1e-06</v>
+        <v>0.01</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
@@ -1505,7 +1505,7 @@
         <v>0</v>
       </c>
       <c r="L13" t="n">
-        <v>1e-06</v>
+        <v>0.01</v>
       </c>
       <c r="M13" t="n">
         <v>12</v>
@@ -1517,28 +1517,28 @@
         <v>38</v>
       </c>
       <c r="P13" t="n">
-        <v>3.571793647959566</v>
+        <v>3.416677426357614</v>
       </c>
       <c r="Q13" t="n">
-        <v>5.423082023326805</v>
+        <v>6.426224317335607</v>
       </c>
       <c r="R13" t="n">
-        <v>0.8535269334684016</v>
+        <v>0.7791419007326796</v>
       </c>
       <c r="S13" t="n">
-        <v>0.9210526315789473</v>
+        <v>0.8157894736842105</v>
       </c>
       <c r="T13" t="n">
-        <v>2.737325207851953</v>
+        <v>2.867285899030742</v>
       </c>
       <c r="U13" t="n">
-        <v>-180.9592623975807</v>
+        <v>-167.7599030436199</v>
       </c>
       <c r="V13" t="n">
-        <v>-118.4005400727027</v>
+        <v>-111.7711384944986</v>
       </c>
       <c r="W13" t="n">
-        <v>-62.55872232487803</v>
+        <v>-55.98876454912136</v>
       </c>
     </row>
     <row r="14">
@@ -1556,7 +1556,7 @@
         <v>0</v>
       </c>
       <c r="D14" t="n">
-        <v>1e-06</v>
+        <v>0.01</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
@@ -1588,7 +1588,7 @@
         <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>1e-06</v>
+        <v>0.01</v>
       </c>
       <c r="M14" t="n">
         <v>13</v>
@@ -1600,28 +1600,28 @@
         <v>38</v>
       </c>
       <c r="P14" t="n">
-        <v>2.754345202046309</v>
+        <v>3.051845049457989</v>
       </c>
       <c r="Q14" t="n">
-        <v>3.751667581709983</v>
+        <v>4.311073244524787</v>
       </c>
       <c r="R14" t="n">
-        <v>0.9197412416631177</v>
+        <v>0.8931971991269569</v>
       </c>
       <c r="S14" t="n">
-        <v>0.8157894736842105</v>
+        <v>0.7631578947368421</v>
       </c>
       <c r="T14" t="n">
-        <v>2.694031659801693</v>
+        <v>2.89932505733121</v>
       </c>
       <c r="U14" t="n">
-        <v>-179.5036474422358</v>
+        <v>-183.0031959547572</v>
       </c>
       <c r="V14" t="n">
-        <v>-120.9752128699639</v>
+        <v>-124.9189872206814</v>
       </c>
       <c r="W14" t="n">
-        <v>-58.52843457227186</v>
+        <v>-58.08420873407576</v>
       </c>
     </row>
     <row r="15">
@@ -1639,7 +1639,7 @@
         <v>0</v>
       </c>
       <c r="D15" t="n">
-        <v>1e-06</v>
+        <v>0.01</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
@@ -1671,7 +1671,7 @@
         <v>0</v>
       </c>
       <c r="L15" t="n">
-        <v>1e-06</v>
+        <v>0.01</v>
       </c>
       <c r="M15" t="n">
         <v>14</v>
@@ -1683,28 +1683,28 @@
         <v>38</v>
       </c>
       <c r="P15" t="n">
-        <v>3.977463275982398</v>
+        <v>2.72082670145035</v>
       </c>
       <c r="Q15" t="n">
-        <v>6.512242099005349</v>
+        <v>4.107066258627672</v>
       </c>
       <c r="R15" t="n">
-        <v>0.8009137779700037</v>
+        <v>0.9240941661010925</v>
       </c>
       <c r="S15" t="n">
-        <v>0.868421052631579</v>
+        <v>0.9210526315789473</v>
       </c>
       <c r="T15" t="n">
-        <v>3.010461229416753</v>
+        <v>2.740234278390495</v>
       </c>
       <c r="U15" t="n">
-        <v>-177.257136531552</v>
+        <v>-181.9696361334692</v>
       </c>
       <c r="V15" t="n">
-        <v>-120.725211934872</v>
+        <v>-120.2685360323843</v>
       </c>
       <c r="W15" t="n">
-        <v>-56.53192459668004</v>
+        <v>-61.70110010108488</v>
       </c>
     </row>
     <row r="16">
@@ -1722,7 +1722,7 @@
         <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>1e-06</v>
+        <v>0.01</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
@@ -1754,7 +1754,7 @@
         <v>0</v>
       </c>
       <c r="L16" t="n">
-        <v>1e-06</v>
+        <v>0.01</v>
       </c>
       <c r="M16" t="n">
         <v>15</v>
@@ -1766,28 +1766,28 @@
         <v>38</v>
       </c>
       <c r="P16" t="n">
-        <v>4.041879918901512</v>
+        <v>4.181731956448925</v>
       </c>
       <c r="Q16" t="n">
-        <v>6.982675116485544</v>
+        <v>6.954094463969433</v>
       </c>
       <c r="R16" t="n">
-        <v>0.7215295855243807</v>
+        <v>0.7146067874229716</v>
       </c>
       <c r="S16" t="n">
-        <v>0.8157894736842105</v>
+        <v>0.7894736842105263</v>
       </c>
       <c r="T16" t="n">
-        <v>3.744722198596475</v>
+        <v>3.916363545959896</v>
       </c>
       <c r="U16" t="n">
-        <v>-159.5259434017546</v>
+        <v>-157.045761779032</v>
       </c>
       <c r="V16" t="n">
-        <v>-117.6524711926408</v>
+        <v>-117.2785126595751</v>
       </c>
       <c r="W16" t="n">
-        <v>-41.8734722091138</v>
+        <v>-39.76724911945689</v>
       </c>
     </row>
     <row r="17">
@@ -1805,7 +1805,7 @@
         <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>1e-06</v>
+        <v>0.01</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
@@ -1837,7 +1837,7 @@
         <v>0</v>
       </c>
       <c r="L17" t="n">
-        <v>1e-06</v>
+        <v>0.01</v>
       </c>
       <c r="M17" t="n">
         <v>16</v>
@@ -1849,28 +1849,28 @@
         <v>38</v>
       </c>
       <c r="P17" t="n">
-        <v>4.284745217754694</v>
+        <v>4.453141336109529</v>
       </c>
       <c r="Q17" t="n">
-        <v>7.834425041964809</v>
+        <v>7.321076520218012</v>
       </c>
       <c r="R17" t="n">
-        <v>0.6840595883705631</v>
+        <v>0.7121898722236659</v>
       </c>
       <c r="S17" t="n">
-        <v>0.868421052631579</v>
+        <v>0.7631578947368421</v>
       </c>
       <c r="T17" t="n">
-        <v>3.358502406448152</v>
+        <v>3.937082943182012</v>
       </c>
       <c r="U17" t="n">
-        <v>-159.2667668798931</v>
+        <v>-145.4357857242302</v>
       </c>
       <c r="V17" t="n">
-        <v>-112.3898227810688</v>
+        <v>-104.3078773675854</v>
       </c>
       <c r="W17" t="n">
-        <v>-46.87694409882424</v>
+        <v>-41.12790835664484</v>
       </c>
     </row>
     <row r="18">
@@ -1888,7 +1888,7 @@
         <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>1e-06</v>
+        <v>0.01</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
@@ -1920,7 +1920,7 @@
         <v>0</v>
       </c>
       <c r="L18" t="n">
-        <v>1e-06</v>
+        <v>0.01</v>
       </c>
       <c r="M18" t="n">
         <v>17</v>
@@ -1932,28 +1932,28 @@
         <v>38</v>
       </c>
       <c r="P18" t="n">
-        <v>3.553763929321206</v>
+        <v>4.100473589531927</v>
       </c>
       <c r="Q18" t="n">
-        <v>4.530019767499992</v>
+        <v>5.59680905656283</v>
       </c>
       <c r="R18" t="n">
-        <v>0.9074109839490965</v>
+        <v>0.8649232535003405</v>
       </c>
       <c r="S18" t="n">
         <v>0.8421052631578947</v>
       </c>
       <c r="T18" t="n">
-        <v>2.886593275250503</v>
+        <v>3.142008983637111</v>
       </c>
       <c r="U18" t="n">
-        <v>-167.0573665229007</v>
+        <v>-172.5883491864834</v>
       </c>
       <c r="V18" t="n">
-        <v>-114.7068722071824</v>
+        <v>-120.5175549132055</v>
       </c>
       <c r="W18" t="n">
-        <v>-52.35049431571824</v>
+        <v>-52.0707942732778</v>
       </c>
     </row>
     <row r="19">
@@ -1971,7 +1971,7 @@
         <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>1e-06</v>
+        <v>0.01</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
@@ -2003,7 +2003,7 @@
         <v>0</v>
       </c>
       <c r="L19" t="n">
-        <v>1e-06</v>
+        <v>0.01</v>
       </c>
       <c r="M19" t="n">
         <v>18</v>
@@ -2015,28 +2015,28 @@
         <v>38</v>
       </c>
       <c r="P19" t="n">
-        <v>2.698742066223183</v>
+        <v>3.021933956515006</v>
       </c>
       <c r="Q19" t="n">
-        <v>4.107623284964235</v>
+        <v>4.399779561505094</v>
       </c>
       <c r="R19" t="n">
-        <v>0.9123212938357756</v>
+        <v>0.8907626882555109</v>
       </c>
       <c r="S19" t="n">
-        <v>0.8421052631578947</v>
+        <v>0.7894736842105263</v>
       </c>
       <c r="T19" t="n">
-        <v>2.820812751538975</v>
+        <v>3.082135875223788</v>
       </c>
       <c r="U19" t="n">
-        <v>-173.3188708923629</v>
+        <v>-170.3731747924571</v>
       </c>
       <c r="V19" t="n">
-        <v>-118.053039780645</v>
+        <v>-114.5591734072765</v>
       </c>
       <c r="W19" t="n">
-        <v>-55.26583111171789</v>
+        <v>-55.81400138518057</v>
       </c>
     </row>
     <row r="20">
@@ -2054,7 +2054,7 @@
         <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>1e-06</v>
+        <v>0.01</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
@@ -2086,7 +2086,7 @@
         <v>0</v>
       </c>
       <c r="L20" t="n">
-        <v>1e-06</v>
+        <v>0.01</v>
       </c>
       <c r="M20" t="n">
         <v>19</v>
@@ -2098,28 +2098,28 @@
         <v>38</v>
       </c>
       <c r="P20" t="n">
-        <v>4.133205247522888</v>
+        <v>3.266511269320639</v>
       </c>
       <c r="Q20" t="n">
-        <v>6.444711436429952</v>
+        <v>4.973878624972825</v>
       </c>
       <c r="R20" t="n">
-        <v>0.7866562469377812</v>
+        <v>0.8726179086056995</v>
       </c>
       <c r="S20" t="n">
-        <v>0.8421052631578947</v>
+        <v>0.7631578947368421</v>
       </c>
       <c r="T20" t="n">
-        <v>2.97550977747442</v>
+        <v>3.071242003530152</v>
       </c>
       <c r="U20" t="n">
-        <v>-185.6802393079883</v>
+        <v>-184.8066720445819</v>
       </c>
       <c r="V20" t="n">
-        <v>-122.8394096077553</v>
+        <v>-121.3224230073326</v>
       </c>
       <c r="W20" t="n">
-        <v>-62.84082970023297</v>
+        <v>-63.48424903724923</v>
       </c>
     </row>
     <row r="21">
@@ -2137,7 +2137,7 @@
         <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>1e-06</v>
+        <v>0.01</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
@@ -2169,7 +2169,7 @@
         <v>0</v>
       </c>
       <c r="L21" t="n">
-        <v>1e-06</v>
+        <v>0.01</v>
       </c>
       <c r="M21" t="n">
         <v>20</v>
@@ -2181,28 +2181,28 @@
         <v>38</v>
       </c>
       <c r="P21" t="n">
-        <v>3.572834045481146</v>
+        <v>3.666968168136867</v>
       </c>
       <c r="Q21" t="n">
-        <v>4.835933321707163</v>
+        <v>6.274119108517319</v>
       </c>
       <c r="R21" t="n">
-        <v>0.8683017202823321</v>
+        <v>0.7876484041805825</v>
       </c>
       <c r="S21" t="n">
-        <v>0.8947368421052632</v>
+        <v>0.8421052631578947</v>
       </c>
       <c r="T21" t="n">
-        <v>2.972442147679018</v>
+        <v>2.836832169486991</v>
       </c>
       <c r="U21" t="n">
-        <v>-172.0210250189384</v>
+        <v>-175.7314501365888</v>
       </c>
       <c r="V21" t="n">
-        <v>-117.3935710499493</v>
+        <v>-120.3501762129174</v>
       </c>
       <c r="W21" t="n">
-        <v>-54.62745396898902</v>
+        <v>-55.38127392367144</v>
       </c>
     </row>
     <row r="22">
@@ -2220,7 +2220,7 @@
         <v>0</v>
       </c>
       <c r="D22" t="n">
-        <v>1e-06</v>
+        <v>0.01</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
@@ -2252,7 +2252,7 @@
         <v>0</v>
       </c>
       <c r="L22" t="n">
-        <v>1e-06</v>
+        <v>0.01</v>
       </c>
       <c r="M22" t="n">
         <v>21</v>
@@ -2264,28 +2264,28 @@
         <v>38</v>
       </c>
       <c r="P22" t="n">
-        <v>4.521548951343351</v>
+        <v>4.94171265849552</v>
       </c>
       <c r="Q22" t="n">
-        <v>7.114153023127278</v>
+        <v>7.808950673926466</v>
       </c>
       <c r="R22" t="n">
-        <v>0.7200300367142678</v>
+        <v>0.6998214830060777</v>
       </c>
       <c r="S22" t="n">
-        <v>0.7894736842105263</v>
+        <v>0.7368421052631579</v>
       </c>
       <c r="T22" t="n">
-        <v>3.816482570930702</v>
+        <v>4.283741681703817</v>
       </c>
       <c r="U22" t="n">
-        <v>-162.7398433823131</v>
+        <v>-160.9283766682806</v>
       </c>
       <c r="V22" t="n">
-        <v>-118.8549661387329</v>
+        <v>-119.5289950840126</v>
       </c>
       <c r="W22" t="n">
-        <v>-43.88487724358021</v>
+        <v>-41.39938158426806</v>
       </c>
     </row>
     <row r="23">
@@ -2303,7 +2303,7 @@
         <v>0</v>
       </c>
       <c r="D23" t="n">
-        <v>1e-06</v>
+        <v>0.01</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
@@ -2335,7 +2335,7 @@
         <v>0</v>
       </c>
       <c r="L23" t="n">
-        <v>1e-06</v>
+        <v>0.01</v>
       </c>
       <c r="M23" t="n">
         <v>22</v>
@@ -2347,28 +2347,28 @@
         <v>38</v>
       </c>
       <c r="P23" t="n">
-        <v>5.263448955131425</v>
+        <v>3.168643331796517</v>
       </c>
       <c r="Q23" t="n">
-        <v>11.23933479666314</v>
+        <v>5.265548833674759</v>
       </c>
       <c r="R23" t="n">
-        <v>0.4637916064583878</v>
+        <v>0.868710272152897</v>
       </c>
       <c r="S23" t="n">
-        <v>0.7894736842105263</v>
+        <v>0.8157894736842105</v>
       </c>
       <c r="T23" t="n">
-        <v>3.739648107667581</v>
+        <v>3.14258761257914</v>
       </c>
       <c r="U23" t="n">
-        <v>-168.1635056458694</v>
+        <v>-177.1199071796054</v>
       </c>
       <c r="V23" t="n">
-        <v>-115.987011787222</v>
+        <v>-116.4891273557231</v>
       </c>
       <c r="W23" t="n">
-        <v>-52.17649385864739</v>
+        <v>-60.63077982388226</v>
       </c>
     </row>
     <row r="24">
@@ -2386,7 +2386,7 @@
         <v>0</v>
       </c>
       <c r="D24" t="n">
-        <v>1e-06</v>
+        <v>0.01</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
@@ -2418,7 +2418,7 @@
         <v>0</v>
       </c>
       <c r="L24" t="n">
-        <v>1e-06</v>
+        <v>0.01</v>
       </c>
       <c r="M24" t="n">
         <v>23</v>
@@ -2430,28 +2430,28 @@
         <v>38</v>
       </c>
       <c r="P24" t="n">
-        <v>2.576906162323855</v>
+        <v>2.549106103900518</v>
       </c>
       <c r="Q24" t="n">
-        <v>4.082780294111188</v>
+        <v>3.731568138388827</v>
       </c>
       <c r="R24" t="n">
-        <v>0.9087975060402698</v>
+        <v>0.9208978764579936</v>
       </c>
       <c r="S24" t="n">
         <v>0.9210526315789473</v>
       </c>
       <c r="T24" t="n">
-        <v>2.738288221972324</v>
+        <v>2.725129196638743</v>
       </c>
       <c r="U24" t="n">
-        <v>-171.5822155146862</v>
+        <v>-171.0770000348843</v>
       </c>
       <c r="V24" t="n">
-        <v>-114.0927483742202</v>
+        <v>-114.1323172217731</v>
       </c>
       <c r="W24" t="n">
-        <v>-57.48946714046605</v>
+        <v>-56.94468281311117</v>
       </c>
     </row>
     <row r="25">
@@ -2469,7 +2469,7 @@
         <v>0</v>
       </c>
       <c r="D25" t="n">
-        <v>1e-06</v>
+        <v>0.01</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
@@ -2501,7 +2501,7 @@
         <v>0</v>
       </c>
       <c r="L25" t="n">
-        <v>1e-06</v>
+        <v>0.01</v>
       </c>
       <c r="M25" t="n">
         <v>24</v>
@@ -2513,28 +2513,28 @@
         <v>38</v>
       </c>
       <c r="P25" t="n">
-        <v>3.719127084110701</v>
+        <v>4.912495162463125</v>
       </c>
       <c r="Q25" t="n">
-        <v>5.530752375893494</v>
+        <v>7.562022466537921</v>
       </c>
       <c r="R25" t="n">
-        <v>0.8325531528015699</v>
+        <v>0.7113024523807886</v>
       </c>
       <c r="S25" t="n">
-        <v>0.9210526315789473</v>
+        <v>0.8421052631578947</v>
       </c>
       <c r="T25" t="n">
-        <v>2.798906086734803</v>
+        <v>3.028424040876993</v>
       </c>
       <c r="U25" t="n">
-        <v>-181.6221176726834</v>
+        <v>-179.3422687772491</v>
       </c>
       <c r="V25" t="n">
-        <v>-123.1697216824441</v>
+        <v>-123.7089508651915</v>
       </c>
       <c r="W25" t="n">
-        <v>-58.45239599023927</v>
+        <v>-55.63331791205766</v>
       </c>
     </row>
     <row r="26">
@@ -2552,7 +2552,7 @@
         <v>0</v>
       </c>
       <c r="D26" t="n">
-        <v>1e-06</v>
+        <v>0.01</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
@@ -2584,7 +2584,7 @@
         <v>0</v>
       </c>
       <c r="L26" t="n">
-        <v>1e-06</v>
+        <v>0.01</v>
       </c>
       <c r="M26" t="n">
         <v>25</v>
@@ -2596,28 +2596,28 @@
         <v>38</v>
       </c>
       <c r="P26" t="n">
-        <v>3.851190468551333</v>
+        <v>3.054360019776816</v>
       </c>
       <c r="Q26" t="n">
-        <v>5.505331024500489</v>
+        <v>4.0935826133603</v>
       </c>
       <c r="R26" t="n">
-        <v>0.8319956348078246</v>
+        <v>0.9026398009030189</v>
       </c>
       <c r="S26" t="n">
         <v>0.7894736842105263</v>
       </c>
       <c r="T26" t="n">
-        <v>3.102719874871876</v>
+        <v>2.980119281822857</v>
       </c>
       <c r="U26" t="n">
-        <v>-174.5084346235284</v>
+        <v>-170.1068882278423</v>
       </c>
       <c r="V26" t="n">
-        <v>-118.3639831766991</v>
+        <v>-114.7548690687979</v>
       </c>
       <c r="W26" t="n">
-        <v>-56.14445144682924</v>
+        <v>-55.35201915904442</v>
       </c>
     </row>
     <row r="27">
@@ -2635,7 +2635,7 @@
         <v>0</v>
       </c>
       <c r="D27" t="n">
-        <v>1e-06</v>
+        <v>0.01</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
@@ -2667,7 +2667,7 @@
         <v>0</v>
       </c>
       <c r="L27" t="n">
-        <v>1e-06</v>
+        <v>0.01</v>
       </c>
       <c r="M27" t="n">
         <v>26</v>
@@ -2679,28 +2679,28 @@
         <v>38</v>
       </c>
       <c r="P27" t="n">
-        <v>5.013623546558549</v>
+        <v>4.017825798446564</v>
       </c>
       <c r="Q27" t="n">
-        <v>9.797115128581934</v>
+        <v>6.743204963190506</v>
       </c>
       <c r="R27" t="n">
-        <v>0.623027874003115</v>
+        <v>0.8092534903661632</v>
       </c>
       <c r="S27" t="n">
-        <v>0.868421052631579</v>
+        <v>0.7368421052631579</v>
       </c>
       <c r="T27" t="n">
-        <v>3.815021093804668</v>
+        <v>3.903352485412991</v>
       </c>
       <c r="U27" t="n">
-        <v>-159.4756324571932</v>
+        <v>-170.3649207334929</v>
       </c>
       <c r="V27" t="n">
-        <v>-116.7779627424004</v>
+        <v>-121.3059508255073</v>
       </c>
       <c r="W27" t="n">
-        <v>-42.69766971479272</v>
+        <v>-49.05896990798561</v>
       </c>
     </row>
     <row r="28">
@@ -2718,7 +2718,7 @@
         <v>0</v>
       </c>
       <c r="D28" t="n">
-        <v>1e-06</v>
+        <v>0.01</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
@@ -2750,7 +2750,7 @@
         <v>0</v>
       </c>
       <c r="L28" t="n">
-        <v>1e-06</v>
+        <v>0.01</v>
       </c>
       <c r="M28" t="n">
         <v>27</v>
@@ -2762,28 +2762,28 @@
         <v>38</v>
       </c>
       <c r="P28" t="n">
-        <v>3.433728319099612</v>
+        <v>3.323885204834498</v>
       </c>
       <c r="Q28" t="n">
-        <v>4.440101855785352</v>
+        <v>4.388664199176995</v>
       </c>
       <c r="R28" t="n">
-        <v>0.885769613973953</v>
+        <v>0.8874853945006766</v>
       </c>
       <c r="S28" t="n">
-        <v>0.8157894736842105</v>
+        <v>0.7631578947368421</v>
       </c>
       <c r="T28" t="n">
-        <v>3.007329318170316</v>
+        <v>3.079111492108765</v>
       </c>
       <c r="U28" t="n">
-        <v>-176.3045888196323</v>
+        <v>-177.2655704317308</v>
       </c>
       <c r="V28" t="n">
-        <v>-119.9791580216323</v>
+        <v>-119.0726894310117</v>
       </c>
       <c r="W28" t="n">
-        <v>-56.32543079800001</v>
+        <v>-58.19288100071911</v>
       </c>
     </row>
     <row r="29">
@@ -2801,7 +2801,7 @@
         <v>0</v>
       </c>
       <c r="D29" t="n">
-        <v>1e-06</v>
+        <v>0.01</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
@@ -2833,7 +2833,7 @@
         <v>0</v>
       </c>
       <c r="L29" t="n">
-        <v>1e-06</v>
+        <v>0.01</v>
       </c>
       <c r="M29" t="n">
         <v>28</v>
@@ -2845,28 +2845,28 @@
         <v>38</v>
       </c>
       <c r="P29" t="n">
-        <v>3.543668044478918</v>
+        <v>3.187640688566834</v>
       </c>
       <c r="Q29" t="n">
-        <v>4.836966360020576</v>
+        <v>4.101960044976395</v>
       </c>
       <c r="R29" t="n">
-        <v>0.8508864043913977</v>
+        <v>0.8983289490738209</v>
       </c>
       <c r="S29" t="n">
         <v>0.868421052631579</v>
       </c>
       <c r="T29" t="n">
-        <v>2.969316247882448</v>
+        <v>2.814618363764942</v>
       </c>
       <c r="U29" t="n">
-        <v>-174.728820117544</v>
+        <v>-174.2218348185184</v>
       </c>
       <c r="V29" t="n">
-        <v>-119.2972950647631</v>
+        <v>-118.5984827022641</v>
       </c>
       <c r="W29" t="n">
-        <v>-55.4315250527809</v>
+        <v>-55.6233521162543</v>
       </c>
     </row>
     <row r="30">
@@ -2884,7 +2884,7 @@
         <v>0</v>
       </c>
       <c r="D30" t="n">
-        <v>1e-06</v>
+        <v>0.01</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
@@ -2916,7 +2916,7 @@
         <v>0</v>
       </c>
       <c r="L30" t="n">
-        <v>1e-06</v>
+        <v>0.01</v>
       </c>
       <c r="M30" t="n">
         <v>29</v>
@@ -2928,28 +2928,28 @@
         <v>38</v>
       </c>
       <c r="P30" t="n">
-        <v>3.268634000117297</v>
+        <v>2.622783030121734</v>
       </c>
       <c r="Q30" t="n">
-        <v>4.810701174036105</v>
+        <v>3.423758895406687</v>
       </c>
       <c r="R30" t="n">
-        <v>0.8869453286177135</v>
+        <v>0.9406351548704109</v>
       </c>
       <c r="S30" t="n">
-        <v>0.868421052631579</v>
+        <v>0.8421052631578947</v>
       </c>
       <c r="T30" t="n">
-        <v>2.865751317772214</v>
+        <v>2.783703362421207</v>
       </c>
       <c r="U30" t="n">
-        <v>-181.464854881661</v>
+        <v>-185.7589214412968</v>
       </c>
       <c r="V30" t="n">
-        <v>-121.279090901314</v>
+        <v>-120.5807804073039</v>
       </c>
       <c r="W30" t="n">
-        <v>-60.18576398034706</v>
+        <v>-65.17814103399292</v>
       </c>
     </row>
     <row r="31">
@@ -2967,7 +2967,7 @@
         <v>0</v>
       </c>
       <c r="D31" t="n">
-        <v>1e-06</v>
+        <v>0.01</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
@@ -2999,7 +2999,7 @@
         <v>0</v>
       </c>
       <c r="L31" t="n">
-        <v>1e-06</v>
+        <v>0.01</v>
       </c>
       <c r="M31" t="n">
         <v>30</v>
@@ -3011,28 +3011,28 @@
         <v>38</v>
       </c>
       <c r="P31" t="n">
-        <v>3.102456811176633</v>
+        <v>3.805860301232553</v>
       </c>
       <c r="Q31" t="n">
-        <v>4.005651243294942</v>
+        <v>6.453761077685891</v>
       </c>
       <c r="R31" t="n">
-        <v>0.9212892735164003</v>
+        <v>0.8160037062742561</v>
       </c>
       <c r="S31" t="n">
-        <v>0.9473684210526315</v>
+        <v>0.8157894736842105</v>
       </c>
       <c r="T31" t="n">
-        <v>2.777769801530548</v>
+        <v>2.955552824383202</v>
       </c>
       <c r="U31" t="n">
-        <v>-171.4597425489678</v>
+        <v>-160.6933601583246</v>
       </c>
       <c r="V31" t="n">
-        <v>-114.6862859542542</v>
+        <v>-112.0079699841062</v>
       </c>
       <c r="W31" t="n">
-        <v>-56.77345659471359</v>
+        <v>-48.68539017421837</v>
       </c>
     </row>
     <row r="32">
@@ -3050,7 +3050,7 @@
         <v>0</v>
       </c>
       <c r="D32" t="n">
-        <v>1e-06</v>
+        <v>0.01</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
@@ -3082,7 +3082,7 @@
         <v>0</v>
       </c>
       <c r="L32" t="n">
-        <v>1e-06</v>
+        <v>0.01</v>
       </c>
       <c r="M32" t="n">
         <v>31</v>
@@ -3094,28 +3094,28 @@
         <v>38</v>
       </c>
       <c r="P32" t="n">
-        <v>2.82457450699174</v>
+        <v>2.868265734545809</v>
       </c>
       <c r="Q32" t="n">
-        <v>3.489274337405615</v>
+        <v>3.589520386324124</v>
       </c>
       <c r="R32" t="n">
-        <v>0.925482563056465</v>
+        <v>0.9301474581223179</v>
       </c>
       <c r="S32" t="n">
-        <v>0.8947368421052632</v>
+        <v>0.868421052631579</v>
       </c>
       <c r="T32" t="n">
-        <v>2.787387796275429</v>
+        <v>2.893769567987529</v>
       </c>
       <c r="U32" t="n">
-        <v>-179.4871449339598</v>
+        <v>-178.7130952151734</v>
       </c>
       <c r="V32" t="n">
-        <v>-119.7864713472309</v>
+        <v>-118.9675564081152</v>
       </c>
       <c r="W32" t="n">
-        <v>-59.70067358672891</v>
+        <v>-59.74553880705821</v>
       </c>
     </row>
     <row r="33">
@@ -3133,7 +3133,7 @@
         <v>0</v>
       </c>
       <c r="D33" t="n">
-        <v>1e-06</v>
+        <v>0.01</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
@@ -3165,7 +3165,7 @@
         <v>0</v>
       </c>
       <c r="L33" t="n">
-        <v>1e-06</v>
+        <v>0.01</v>
       </c>
       <c r="M33" t="n">
         <v>32</v>
@@ -3177,28 +3177,28 @@
         <v>38</v>
       </c>
       <c r="P33" t="n">
-        <v>2.358719663183115</v>
+        <v>3.396968448796584</v>
       </c>
       <c r="Q33" t="n">
-        <v>3.053303949646089</v>
+        <v>5.224245591689992</v>
       </c>
       <c r="R33" t="n">
-        <v>0.9522533168150162</v>
+        <v>0.8538865377834979</v>
       </c>
       <c r="S33" t="n">
-        <v>0.9473684210526315</v>
+        <v>0.8947368421052632</v>
       </c>
       <c r="T33" t="n">
-        <v>2.587756742279073</v>
+        <v>3.163474640799208</v>
       </c>
       <c r="U33" t="n">
-        <v>-178.1683601730826</v>
+        <v>-169.5025670392639</v>
       </c>
       <c r="V33" t="n">
-        <v>-123.3208467823572</v>
+        <v>-119.8424025479335</v>
       </c>
       <c r="W33" t="n">
-        <v>-54.84751339072535</v>
+        <v>-49.66016449133041</v>
       </c>
     </row>
     <row r="34">
@@ -3216,7 +3216,7 @@
         <v>0</v>
       </c>
       <c r="D34" t="n">
-        <v>1e-06</v>
+        <v>0.01</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
@@ -3248,7 +3248,7 @@
         <v>0</v>
       </c>
       <c r="L34" t="n">
-        <v>1e-06</v>
+        <v>0.01</v>
       </c>
       <c r="M34" t="n">
         <v>33</v>
@@ -3260,28 +3260,28 @@
         <v>38</v>
       </c>
       <c r="P34" t="n">
-        <v>4.933624870971811</v>
+        <v>4.393215793490469</v>
       </c>
       <c r="Q34" t="n">
-        <v>9.268802053871807</v>
+        <v>6.27399067565282</v>
       </c>
       <c r="R34" t="n">
-        <v>0.5757685990815465</v>
+        <v>0.7907760984308658</v>
       </c>
       <c r="S34" t="n">
-        <v>0.8157894736842105</v>
+        <v>0.7368421052631579</v>
       </c>
       <c r="T34" t="n">
-        <v>3.816891177573138</v>
+        <v>3.749000799889642</v>
       </c>
       <c r="U34" t="n">
-        <v>-148.4070938326524</v>
+        <v>-150.3868504053956</v>
       </c>
       <c r="V34" t="n">
-        <v>-114.1313857422489</v>
+        <v>-111.0656641705154</v>
       </c>
       <c r="W34" t="n">
-        <v>-34.27570809040355</v>
+        <v>-39.3211862348802</v>
       </c>
     </row>
     <row r="35">
@@ -3299,7 +3299,7 @@
         <v>0</v>
       </c>
       <c r="D35" t="n">
-        <v>1e-06</v>
+        <v>0.01</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
@@ -3331,7 +3331,7 @@
         <v>0</v>
       </c>
       <c r="L35" t="n">
-        <v>1e-06</v>
+        <v>0.01</v>
       </c>
       <c r="M35" t="n">
         <v>34</v>
@@ -3343,28 +3343,28 @@
         <v>38</v>
       </c>
       <c r="P35" t="n">
-        <v>3.72790955600955</v>
+        <v>3.346644687527275</v>
       </c>
       <c r="Q35" t="n">
-        <v>5.056403901374706</v>
+        <v>4.327154190512665</v>
       </c>
       <c r="R35" t="n">
-        <v>0.8494696061529554</v>
+        <v>0.8974739011745937</v>
       </c>
       <c r="S35" t="n">
-        <v>0.7368421052631579</v>
+        <v>0.8157894736842105</v>
       </c>
       <c r="T35" t="n">
-        <v>3.072516109022472</v>
+        <v>2.813426575343128</v>
       </c>
       <c r="U35" t="n">
-        <v>-178.3686430243629</v>
+        <v>-178.0937685553393</v>
       </c>
       <c r="V35" t="n">
-        <v>-118.1614746328462</v>
+        <v>-115.1005052143945</v>
       </c>
       <c r="W35" t="n">
-        <v>-60.20716839151675</v>
+        <v>-62.99326334094479</v>
       </c>
     </row>
     <row r="36">
@@ -3382,7 +3382,7 @@
         <v>0</v>
       </c>
       <c r="D36" t="n">
-        <v>1e-06</v>
+        <v>0.01</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
@@ -3414,7 +3414,7 @@
         <v>0</v>
       </c>
       <c r="L36" t="n">
-        <v>1e-06</v>
+        <v>0.01</v>
       </c>
       <c r="M36" t="n">
         <v>35</v>
@@ -3426,28 +3426,28 @@
         <v>38</v>
       </c>
       <c r="P36" t="n">
-        <v>3.423636231924905</v>
+        <v>3.605583779191219</v>
       </c>
       <c r="Q36" t="n">
-        <v>5.841710426394133</v>
+        <v>6.657908851010693</v>
       </c>
       <c r="R36" t="n">
-        <v>0.8687026322964602</v>
+        <v>0.8254866489268203</v>
       </c>
       <c r="S36" t="n">
-        <v>0.9210526315789473</v>
+        <v>0.868421052631579</v>
       </c>
       <c r="T36" t="n">
-        <v>2.803303333494314</v>
+        <v>2.712817041151506</v>
       </c>
       <c r="U36" t="n">
-        <v>-180.5919326808211</v>
+        <v>-189.3756186504828</v>
       </c>
       <c r="V36" t="n">
-        <v>-115.8808591902952</v>
+        <v>-122.0213334341457</v>
       </c>
       <c r="W36" t="n">
-        <v>-64.71107349052593</v>
+        <v>-67.35428521633708</v>
       </c>
     </row>
     <row r="37">
@@ -3465,7 +3465,7 @@
         <v>0</v>
       </c>
       <c r="D37" t="n">
-        <v>1e-06</v>
+        <v>0.01</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
@@ -3497,7 +3497,7 @@
         <v>0</v>
       </c>
       <c r="L37" t="n">
-        <v>1e-06</v>
+        <v>0.01</v>
       </c>
       <c r="M37" t="n">
         <v>36</v>
@@ -3509,28 +3509,28 @@
         <v>38</v>
       </c>
       <c r="P37" t="n">
-        <v>3.309276831186263</v>
+        <v>2.751696360406907</v>
       </c>
       <c r="Q37" t="n">
-        <v>4.473759913413768</v>
+        <v>4.422279072915088</v>
       </c>
       <c r="R37" t="n">
-        <v>0.9135642516932938</v>
+        <v>0.9115925539492921</v>
       </c>
       <c r="S37" t="n">
-        <v>0.8421052631578947</v>
+        <v>0.9210526315789473</v>
       </c>
       <c r="T37" t="n">
-        <v>2.943484460635739</v>
+        <v>2.673370538486374</v>
       </c>
       <c r="U37" t="n">
-        <v>-182.5704014584505</v>
+        <v>-177.9934093134258</v>
       </c>
       <c r="V37" t="n">
-        <v>-116.8392815859567</v>
+        <v>-115.7680199504</v>
       </c>
       <c r="W37" t="n">
-        <v>-65.73111987249376</v>
+        <v>-62.22538936302584</v>
       </c>
     </row>
     <row r="38">
@@ -3548,7 +3548,7 @@
         <v>0</v>
       </c>
       <c r="D38" t="n">
-        <v>1e-06</v>
+        <v>0.01</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
@@ -3580,7 +3580,7 @@
         <v>0</v>
       </c>
       <c r="L38" t="n">
-        <v>1e-06</v>
+        <v>0.01</v>
       </c>
       <c r="M38" t="n">
         <v>37</v>
@@ -3592,28 +3592,28 @@
         <v>38</v>
       </c>
       <c r="P38" t="n">
-        <v>4.200630309609751</v>
+        <v>4.926369282277081</v>
       </c>
       <c r="Q38" t="n">
-        <v>6.536621907776572</v>
+        <v>7.634986518532897</v>
       </c>
       <c r="R38" t="n">
-        <v>0.7795002004549266</v>
+        <v>0.7203148610877134</v>
       </c>
       <c r="S38" t="n">
-        <v>0.7894736842105263</v>
+        <v>0.7105263157894737</v>
       </c>
       <c r="T38" t="n">
-        <v>3.684320587574697</v>
+        <v>4.028632678496003</v>
       </c>
       <c r="U38" t="n">
-        <v>-181.6885319821872</v>
+        <v>-180.940797398159</v>
       </c>
       <c r="V38" t="n">
-        <v>-120.5025661760531</v>
+        <v>-122.8807724042817</v>
       </c>
       <c r="W38" t="n">
-        <v>-61.18596580613402</v>
+        <v>-58.06002499387722</v>
       </c>
     </row>
     <row r="39">
@@ -3631,7 +3631,7 @@
         <v>0</v>
       </c>
       <c r="D39" t="n">
-        <v>1e-06</v>
+        <v>0.01</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
@@ -3663,7 +3663,7 @@
         <v>0</v>
       </c>
       <c r="L39" t="n">
-        <v>1e-06</v>
+        <v>0.01</v>
       </c>
       <c r="M39" t="n">
         <v>38</v>
@@ -3675,28 +3675,28 @@
         <v>38</v>
       </c>
       <c r="P39" t="n">
-        <v>3.134435618043403</v>
+        <v>3.164581065220867</v>
       </c>
       <c r="Q39" t="n">
-        <v>4.476757490913983</v>
+        <v>4.479645181379914</v>
       </c>
       <c r="R39" t="n">
-        <v>0.9070414453312199</v>
+        <v>0.9096135656260117</v>
       </c>
       <c r="S39" t="n">
-        <v>0.8947368421052632</v>
+        <v>0.8157894736842105</v>
       </c>
       <c r="T39" t="n">
-        <v>2.800007163302804</v>
+        <v>2.80181596620708</v>
       </c>
       <c r="U39" t="n">
-        <v>-180.9794330045086</v>
+        <v>-179.081658362439</v>
       </c>
       <c r="V39" t="n">
-        <v>-120.5942038433649</v>
+        <v>-119.8627692857426</v>
       </c>
       <c r="W39" t="n">
-        <v>-60.38522916114371</v>
+        <v>-59.21888907669636</v>
       </c>
     </row>
     <row r="40">
@@ -3714,7 +3714,7 @@
         <v>0</v>
       </c>
       <c r="D40" t="n">
-        <v>1e-06</v>
+        <v>0.01</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
@@ -3746,7 +3746,7 @@
         <v>0</v>
       </c>
       <c r="L40" t="n">
-        <v>1e-06</v>
+        <v>0.01</v>
       </c>
       <c r="M40" t="n">
         <v>39</v>
@@ -3758,28 +3758,28 @@
         <v>38</v>
       </c>
       <c r="P40" t="n">
-        <v>3.860036118645147</v>
+        <v>3.597476588527453</v>
       </c>
       <c r="Q40" t="n">
-        <v>5.501769920560968</v>
+        <v>4.636918596181915</v>
       </c>
       <c r="R40" t="n">
-        <v>0.8460600023402074</v>
+        <v>0.8902331221017392</v>
       </c>
       <c r="S40" t="n">
-        <v>0.8947368421052632</v>
+        <v>0.7894736842105263</v>
       </c>
       <c r="T40" t="n">
-        <v>3.268574853727669</v>
+        <v>3.670705581526501</v>
       </c>
       <c r="U40" t="n">
-        <v>-157.8572406346431</v>
+        <v>-172.4329545225179</v>
       </c>
       <c r="V40" t="n">
-        <v>-110.5088157962527</v>
+        <v>-116.8867106090656</v>
       </c>
       <c r="W40" t="n">
-        <v>-47.34842483839049</v>
+        <v>-55.5462439134524</v>
       </c>
     </row>
     <row r="41">
@@ -3797,7 +3797,7 @@
         <v>0</v>
       </c>
       <c r="D41" t="n">
-        <v>1e-06</v>
+        <v>0.01</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
@@ -3829,7 +3829,7 @@
         <v>0</v>
       </c>
       <c r="L41" t="n">
-        <v>1e-06</v>
+        <v>0.01</v>
       </c>
       <c r="M41" t="n">
         <v>40</v>
@@ -3841,28 +3841,28 @@
         <v>38</v>
       </c>
       <c r="P41" t="n">
-        <v>4.670501663879577</v>
+        <v>3.778742063173782</v>
       </c>
       <c r="Q41" t="n">
-        <v>8.340374097419447</v>
+        <v>6.706652167794902</v>
       </c>
       <c r="R41" t="n">
-        <v>0.4881444259054787</v>
+        <v>0.6695527785776596</v>
       </c>
       <c r="S41" t="n">
         <v>0.7894736842105263</v>
       </c>
       <c r="T41" t="n">
-        <v>3.610503061464019</v>
+        <v>3.644917588555397</v>
       </c>
       <c r="U41" t="n">
-        <v>-144.8035160230385</v>
+        <v>-146.5890307900787</v>
       </c>
       <c r="V41" t="n">
-        <v>-112.5320738065476</v>
+        <v>-111.7979042295341</v>
       </c>
       <c r="W41" t="n">
-        <v>-32.27144221649085</v>
+        <v>-34.79112656054454</v>
       </c>
     </row>
     <row r="42">
@@ -3880,7 +3880,7 @@
         <v>0</v>
       </c>
       <c r="D42" t="n">
-        <v>1e-06</v>
+        <v>0.01</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
@@ -3912,7 +3912,7 @@
         <v>0</v>
       </c>
       <c r="L42" t="n">
-        <v>1e-06</v>
+        <v>0.01</v>
       </c>
       <c r="M42" t="n">
         <v>41</v>
@@ -3924,28 +3924,28 @@
         <v>38</v>
       </c>
       <c r="P42" t="n">
-        <v>4.605515990375252</v>
+        <v>5.063010404025662</v>
       </c>
       <c r="Q42" t="n">
-        <v>7.426873703722389</v>
+        <v>9.232591575943475</v>
       </c>
       <c r="R42" t="n">
-        <v>0.7388107711644426</v>
+        <v>0.602022050560157</v>
       </c>
       <c r="S42" t="n">
-        <v>0.8421052631578947</v>
+        <v>0.7631578947368421</v>
       </c>
       <c r="T42" t="n">
-        <v>3.636939507764014</v>
+        <v>4.142107008207121</v>
       </c>
       <c r="U42" t="n">
-        <v>-151.4180767030688</v>
+        <v>-161.707731139972</v>
       </c>
       <c r="V42" t="n">
-        <v>-110.4481793011086</v>
+        <v>-119.2611095646295</v>
       </c>
       <c r="W42" t="n">
-        <v>-40.96989740196025</v>
+        <v>-42.44662157534248</v>
       </c>
     </row>
     <row r="43">
@@ -3963,7 +3963,7 @@
         <v>0</v>
       </c>
       <c r="D43" t="n">
-        <v>1e-06</v>
+        <v>0.01</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
@@ -3995,7 +3995,7 @@
         <v>0</v>
       </c>
       <c r="L43" t="n">
-        <v>1e-06</v>
+        <v>0.01</v>
       </c>
       <c r="M43" t="n">
         <v>42</v>
@@ -4007,28 +4007,28 @@
         <v>38</v>
       </c>
       <c r="P43" t="n">
-        <v>4.360657318758679</v>
+        <v>3.623545914758193</v>
       </c>
       <c r="Q43" t="n">
-        <v>6.633442185738816</v>
+        <v>4.636779875207861</v>
       </c>
       <c r="R43" t="n">
-        <v>0.7974658783088027</v>
+        <v>0.900864639862023</v>
       </c>
       <c r="S43" t="n">
-        <v>0.8157894736842105</v>
+        <v>0.868421052631579</v>
       </c>
       <c r="T43" t="n">
-        <v>3.147442653532453</v>
+        <v>3.054678906024832</v>
       </c>
       <c r="U43" t="n">
-        <v>-164.5241745981597</v>
+        <v>-157.9018957287981</v>
       </c>
       <c r="V43" t="n">
-        <v>-112.4422717184679</v>
+        <v>-108.1590096870462</v>
       </c>
       <c r="W43" t="n">
-        <v>-52.08190287969185</v>
+        <v>-49.74288604175189</v>
       </c>
     </row>
     <row r="44">
@@ -4046,7 +4046,7 @@
         <v>0</v>
       </c>
       <c r="D44" t="n">
-        <v>1e-06</v>
+        <v>0.01</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
@@ -4078,7 +4078,7 @@
         <v>0</v>
       </c>
       <c r="L44" t="n">
-        <v>1e-06</v>
+        <v>0.01</v>
       </c>
       <c r="M44" t="n">
         <v>43</v>
@@ -4090,28 +4090,28 @@
         <v>38</v>
       </c>
       <c r="P44" t="n">
-        <v>2.323291065984555</v>
+        <v>2.446809879693505</v>
       </c>
       <c r="Q44" t="n">
-        <v>3.128959429811382</v>
+        <v>3.294438488930388</v>
       </c>
       <c r="R44" t="n">
-        <v>0.9389356395380298</v>
+        <v>0.9177456604800598</v>
       </c>
       <c r="S44" t="n">
-        <v>0.9736842105263158</v>
+        <v>0.9473684210526315</v>
       </c>
       <c r="T44" t="n">
-        <v>2.578395889240152</v>
+        <v>2.605994699567425</v>
       </c>
       <c r="U44" t="n">
-        <v>-183.9881329775364</v>
+        <v>-175.1050099600714</v>
       </c>
       <c r="V44" t="n">
-        <v>-118.7719892558608</v>
+        <v>-115.7884263525465</v>
       </c>
       <c r="W44" t="n">
-        <v>-65.21614372167559</v>
+        <v>-59.31658360752492</v>
       </c>
     </row>
     <row r="45">
@@ -4129,7 +4129,7 @@
         <v>0</v>
       </c>
       <c r="D45" t="n">
-        <v>1e-06</v>
+        <v>0.01</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
@@ -4161,7 +4161,7 @@
         <v>0</v>
       </c>
       <c r="L45" t="n">
-        <v>1e-06</v>
+        <v>0.01</v>
       </c>
       <c r="M45" t="n">
         <v>44</v>
@@ -4173,28 +4173,28 @@
         <v>38</v>
       </c>
       <c r="P45" t="n">
-        <v>3.190814582945696</v>
+        <v>3.279684876879139</v>
       </c>
       <c r="Q45" t="n">
-        <v>4.471002422748362</v>
+        <v>4.489725470214556</v>
       </c>
       <c r="R45" t="n">
-        <v>0.8987606619417577</v>
+        <v>0.9016328066504642</v>
       </c>
       <c r="S45" t="n">
         <v>0.7894736842105263</v>
       </c>
       <c r="T45" t="n">
-        <v>2.973508761243412</v>
+        <v>3.107284510108035</v>
       </c>
       <c r="U45" t="n">
-        <v>-181.6727279097514</v>
+        <v>-186.249125936412</v>
       </c>
       <c r="V45" t="n">
-        <v>-124.5251815149833</v>
+        <v>-124.4952144781082</v>
       </c>
       <c r="W45" t="n">
-        <v>-57.14754639476804</v>
+        <v>-61.75391145830375</v>
       </c>
     </row>
     <row r="46">
@@ -4212,7 +4212,7 @@
         <v>0</v>
       </c>
       <c r="D46" t="n">
-        <v>1e-06</v>
+        <v>0.01</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
@@ -4244,7 +4244,7 @@
         <v>0</v>
       </c>
       <c r="L46" t="n">
-        <v>1e-06</v>
+        <v>0.01</v>
       </c>
       <c r="M46" t="n">
         <v>45</v>
@@ -4256,28 +4256,28 @@
         <v>38</v>
       </c>
       <c r="P46" t="n">
-        <v>3.835278432134094</v>
+        <v>4.432011485665407</v>
       </c>
       <c r="Q46" t="n">
-        <v>5.074392623563073</v>
+        <v>5.960533490396607</v>
       </c>
       <c r="R46" t="n">
-        <v>0.8438322630251305</v>
+        <v>0.7971300087936252</v>
       </c>
       <c r="S46" t="n">
-        <v>0.8157894736842105</v>
+        <v>0.7368421052631579</v>
       </c>
       <c r="T46" t="n">
-        <v>3.152347330234791</v>
+        <v>3.386360003891206</v>
       </c>
       <c r="U46" t="n">
-        <v>-175.8336657520304</v>
+        <v>-169.6422281552906</v>
       </c>
       <c r="V46" t="n">
-        <v>-117.2294859292619</v>
+        <v>-111.282165853814</v>
       </c>
       <c r="W46" t="n">
-        <v>-58.60417982276851</v>
+        <v>-58.3600623014766</v>
       </c>
     </row>
     <row r="47">
@@ -4295,7 +4295,7 @@
         <v>0</v>
       </c>
       <c r="D47" t="n">
-        <v>1e-06</v>
+        <v>0.01</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
@@ -4327,7 +4327,7 @@
         <v>0</v>
       </c>
       <c r="L47" t="n">
-        <v>1e-06</v>
+        <v>0.01</v>
       </c>
       <c r="M47" t="n">
         <v>46</v>
@@ -4339,28 +4339,28 @@
         <v>38</v>
       </c>
       <c r="P47" t="n">
-        <v>3.822061831790383</v>
+        <v>4.38787794130242</v>
       </c>
       <c r="Q47" t="n">
-        <v>5.868422933907697</v>
+        <v>8.547446783408517</v>
       </c>
       <c r="R47" t="n">
-        <v>0.8299965952239698</v>
+        <v>0.6261204636224402</v>
       </c>
       <c r="S47" t="n">
         <v>0.7894736842105263</v>
       </c>
       <c r="T47" t="n">
-        <v>3.402323914546325</v>
+        <v>3.725335492636437</v>
       </c>
       <c r="U47" t="n">
-        <v>-169.3603309482056</v>
+        <v>-169.7714375152898</v>
       </c>
       <c r="V47" t="n">
-        <v>-120.5075201026565</v>
+        <v>-120.1964026477172</v>
       </c>
       <c r="W47" t="n">
-        <v>-48.85281084554919</v>
+        <v>-49.57503486757258</v>
       </c>
     </row>
     <row r="48">
@@ -4378,7 +4378,7 @@
         <v>0</v>
       </c>
       <c r="D48" t="n">
-        <v>1e-06</v>
+        <v>0.01</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
@@ -4410,7 +4410,7 @@
         <v>0</v>
       </c>
       <c r="L48" t="n">
-        <v>1e-06</v>
+        <v>0.01</v>
       </c>
       <c r="M48" t="n">
         <v>47</v>
@@ -4422,28 +4422,28 @@
         <v>38</v>
       </c>
       <c r="P48" t="n">
-        <v>3.81115935225323</v>
+        <v>2.790923014206449</v>
       </c>
       <c r="Q48" t="n">
-        <v>6.20021351282951</v>
+        <v>3.660914179163071</v>
       </c>
       <c r="R48" t="n">
-        <v>0.830949596157591</v>
+        <v>0.942066800228481</v>
       </c>
       <c r="S48" t="n">
-        <v>0.8421052631578947</v>
+        <v>0.9473684210526315</v>
       </c>
       <c r="T48" t="n">
-        <v>3.077378055418757</v>
+        <v>2.713310133206667</v>
       </c>
       <c r="U48" t="n">
-        <v>-168.5715118936408</v>
+        <v>-179.086427216017</v>
       </c>
       <c r="V48" t="n">
-        <v>-114.8459014553602</v>
+        <v>-120.1902815362439</v>
       </c>
       <c r="W48" t="n">
-        <v>-53.7256104382806</v>
+        <v>-58.89614567977306</v>
       </c>
     </row>
     <row r="49">
@@ -4461,7 +4461,7 @@
         <v>0</v>
       </c>
       <c r="D49" t="n">
-        <v>1e-06</v>
+        <v>0.01</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
@@ -4493,7 +4493,7 @@
         <v>0</v>
       </c>
       <c r="L49" t="n">
-        <v>1e-06</v>
+        <v>0.01</v>
       </c>
       <c r="M49" t="n">
         <v>48</v>
@@ -4505,28 +4505,28 @@
         <v>38</v>
       </c>
       <c r="P49" t="n">
-        <v>2.938056994681062</v>
+        <v>3.153508276359513</v>
       </c>
       <c r="Q49" t="n">
-        <v>4.236830715250314</v>
+        <v>4.70475112050753</v>
       </c>
       <c r="R49" t="n">
-        <v>0.9192212691588697</v>
+        <v>0.8933509627960694</v>
       </c>
       <c r="S49" t="n">
-        <v>0.9210526315789473</v>
+        <v>0.8421052631578947</v>
       </c>
       <c r="T49" t="n">
-        <v>2.771426931553299</v>
+        <v>3.100215011296159</v>
       </c>
       <c r="U49" t="n">
-        <v>-176.3246084331486</v>
+        <v>-171.4870108022669</v>
       </c>
       <c r="V49" t="n">
-        <v>-118.4765195548813</v>
+        <v>-117.4878901176557</v>
       </c>
       <c r="W49" t="n">
-        <v>-57.84808887826729</v>
+        <v>-53.99912068461123</v>
       </c>
     </row>
     <row r="50">
@@ -4544,7 +4544,7 @@
         <v>0</v>
       </c>
       <c r="D50" t="n">
-        <v>1e-06</v>
+        <v>0.01</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
@@ -4576,7 +4576,7 @@
         <v>0</v>
       </c>
       <c r="L50" t="n">
-        <v>1e-06</v>
+        <v>0.01</v>
       </c>
       <c r="M50" t="n">
         <v>49</v>
@@ -4588,28 +4588,28 @@
         <v>38</v>
       </c>
       <c r="P50" t="n">
-        <v>2.758587896033683</v>
+        <v>3.702464456880941</v>
       </c>
       <c r="Q50" t="n">
-        <v>4.437434185157229</v>
+        <v>6.160944778745234</v>
       </c>
       <c r="R50" t="n">
-        <v>0.8827461311941454</v>
+        <v>0.7814349806949478</v>
       </c>
       <c r="S50" t="n">
-        <v>0.9210526315789473</v>
+        <v>0.7894736842105263</v>
       </c>
       <c r="T50" t="n">
-        <v>2.745716856625643</v>
+        <v>3.004065870505256</v>
       </c>
       <c r="U50" t="n">
-        <v>-177.3337188190139</v>
+        <v>-176.3134373454546</v>
       </c>
       <c r="V50" t="n">
-        <v>-121.3726031216025</v>
+        <v>-118.8366900428924</v>
       </c>
       <c r="W50" t="n">
-        <v>-55.96111569741147</v>
+        <v>-57.4767473025622</v>
       </c>
     </row>
     <row r="51">
@@ -4627,7 +4627,7 @@
         <v>0</v>
       </c>
       <c r="D51" t="n">
-        <v>1e-06</v>
+        <v>0.01</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
@@ -4659,7 +4659,7 @@
         <v>0</v>
       </c>
       <c r="L51" t="n">
-        <v>1e-06</v>
+        <v>0.01</v>
       </c>
       <c r="M51" t="n">
         <v>50</v>
@@ -4671,28 +4671,28 @@
         <v>38</v>
       </c>
       <c r="P51" t="n">
-        <v>3.626982732747694</v>
+        <v>3.259315643485093</v>
       </c>
       <c r="Q51" t="n">
-        <v>4.502766177679084</v>
+        <v>4.238382134676862</v>
       </c>
       <c r="R51" t="n">
-        <v>0.884293834396514</v>
+        <v>0.9047368167521844</v>
       </c>
       <c r="S51" t="n">
         <v>0.8947368421052632</v>
       </c>
       <c r="T51" t="n">
-        <v>2.899853188300672</v>
+        <v>2.857265295951201</v>
       </c>
       <c r="U51" t="n">
-        <v>-168.8985440072475</v>
+        <v>-170.498317353519</v>
       </c>
       <c r="V51" t="n">
-        <v>-109.7586182999555</v>
+        <v>-110.9343347479874</v>
       </c>
       <c r="W51" t="n">
-        <v>-59.13992570729195</v>
+        <v>-59.56398260553158</v>
       </c>
     </row>
   </sheetData>
